--- a/SGC-CKN/Excel/557c9273-0d7b-4911-b9bf-6f06c21907ce_Hạng_mục__Thi_công_cọc_khoan_nhồi__tường_vây_cho_các_hạng_mục_Lô_CT-02_P1-161_D800_04-04-2026.xlsx
+++ b/SGC-CKN/Excel/557c9273-0d7b-4911-b9bf-6f06c21907ce_Hạng_mục__Thi_công_cọc_khoan_nhồi__tường_vây_cho_các_hạng_mục_Lô_CT-02_P1-161_D800_04-04-2026.xlsx
@@ -179,7 +179,7 @@
   </si>
   <si>
     <t xml:space="preserve">02:25
-04/04/2026</t>
+03/04/2026</t>
   </si>
   <si>
     <t>KTK</t>
